--- a/AAII_Financials/Quarterly/HMN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HMN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>HMN</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>443500</v>
+      </c>
+      <c r="E8" s="3">
         <v>429300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>434800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>438500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>411700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>416400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>409000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>412100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>388100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>386000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>402900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>378700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>356400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>353900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>346700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>349400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>347700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>348500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>332000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>336200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>347100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>325200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>352400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>338100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>625200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>310900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>332500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>336600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>769100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>316100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>278700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>311400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>307400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>295600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>326400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>287200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>285800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>284700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>308300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>272900</v>
+      </c>
+      <c r="E9" s="3">
         <v>262500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>263000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>258200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>266100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>265600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>253500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>274200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>288100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>256200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>260900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>278200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>281300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>255600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>23500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>24600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>50400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>30000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>26200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>26300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>56600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>25000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>30500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>26100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>26600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>26700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>28300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>24200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>24800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>24900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>23600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>170600</v>
+      </c>
+      <c r="E10" s="3">
         <v>166800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>171800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>180300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>145600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>150800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>155500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>137900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>129800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>142000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>98300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>324200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>327200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>326200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>326500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>313300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>323600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>301100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>327500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>313500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>574800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>280900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>306300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>310300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>712500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>291100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>248200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>285300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>268900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>298100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>263000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>261000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>259800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>284700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>262500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,97 +1543,100 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>5100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6800</v>
-      </c>
-      <c r="S14" s="3">
-        <v>1800</v>
       </c>
       <c r="T14" s="3">
         <v>1800</v>
       </c>
       <c r="U14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1100</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>28300</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>200</v>
       </c>
       <c r="AG14" s="3">
         <v>200</v>
       </c>
       <c r="AH14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI14" s="3">
         <v>100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>23400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-5600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-2600</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>25400</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3600</v>
       </c>
       <c r="G15" s="3">
         <v>3600</v>
@@ -1628,13 +1651,13 @@
         <v>3600</v>
       </c>
       <c r="K15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L15" s="3">
         <v>3700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>3700</v>
       </c>
       <c r="N15" s="3">
         <v>3700</v>
@@ -1646,7 +1669,7 @@
         <v>3700</v>
       </c>
       <c r="Q15" s="3">
-        <v>4200</v>
+        <v>3700</v>
       </c>
       <c r="R15" s="3">
         <v>4200</v>
@@ -1658,44 +1681,44 @@
         <v>4200</v>
       </c>
       <c r="U15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V15" s="3">
         <v>3200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>500</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1705,8 +1728,8 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>384900</v>
+      </c>
+      <c r="E17" s="3">
         <v>369600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>379100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>358100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>366600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>360000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>352200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>360700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>374800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>344300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>347100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>357600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>365100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>339100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>366700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>320700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>349400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>319600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>278900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>313800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>285500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>273500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>290300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>289500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>561200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>288200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>287700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>301500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>596900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>274200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>303600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>291100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>297300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>268600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>288200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>250800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>280600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>264000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>278100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>249000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E18" s="3">
         <v>59700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>55700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>80400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>56400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>21100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-20000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>53100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>61600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>62100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>48600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>64000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>22700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>44800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>35100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>172200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>41900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-24900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>20300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>27000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>38200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>36500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>5200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>20700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>30200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,8 +2130,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2174,92 +2208,95 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E21" s="3">
         <v>63300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>59200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>84000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>48700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>60000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>60400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>45300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>24800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>41500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>32700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>54800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>67200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>57200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>67900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>54600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>75700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>56600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2296,31 +2333,34 @@
       <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E22" s="3">
         <v>9500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>8700</v>
       </c>
       <c r="K22" s="3">
         <v>8700</v>
@@ -2329,37 +2369,37 @@
         <v>8700</v>
       </c>
       <c r="M22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N22" s="3">
         <v>8600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3400</v>
-      </c>
-      <c r="W22" s="3">
-        <v>3500</v>
       </c>
       <c r="X22" s="3">
         <v>3500</v>
@@ -2368,25 +2408,25 @@
         <v>3500</v>
       </c>
       <c r="Z22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AA22" s="3">
         <v>3600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6600</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>3300</v>
       </c>
       <c r="AG22" s="3">
         <v>3300</v>
@@ -2398,19 +2438,19 @@
         <v>3300</v>
       </c>
       <c r="AJ22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AK22" s="3">
         <v>3200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>2900</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>3000</v>
       </c>
       <c r="AO22" s="3">
         <v>3000</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>3000</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E23" s="3">
         <v>50200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>71500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>47200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>19000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>58100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>48200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>58600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>45100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>55900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>165500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-28200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>23800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>35100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>33500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>17800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>27200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>9000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-9200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>9100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>39500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-7900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>8800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>6900</v>
       </c>
-      <c r="AM24" s="3">
-        <v>0</v>
-      </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>2500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>7400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E26" s="3">
         <v>41200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>36200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>58300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>38200</v>
       </c>
       <c r="I26" s="3">
         <v>38200</v>
       </c>
       <c r="J26" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K26" s="3">
         <v>34300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>39500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>40500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>46700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>39300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>47800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>36500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>46300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>33000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>25500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>126000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>32200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>20200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>26300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>26600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>15300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>19800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E27" s="3">
         <v>41200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>36200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>58300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>38200</v>
       </c>
       <c r="I27" s="3">
         <v>38200</v>
       </c>
       <c r="J27" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K27" s="3">
         <v>34300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>39500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>40500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>46700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>47800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>36500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>46300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>33000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>25500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>126000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>32200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>26300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>26600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>15300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>19800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3206,8 +3267,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -3218,20 +3279,20 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>2800</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>2800</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>2800</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>99000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,8 +3630,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E33" s="3">
         <v>41200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>36200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>38200</v>
       </c>
       <c r="I33" s="3">
         <v>38200</v>
       </c>
       <c r="J33" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K33" s="3">
         <v>34300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>39500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>40500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>46700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>47800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>36500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>49100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>33000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>25500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>126000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>32200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>125300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>26600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>15300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>19800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E35" s="3">
         <v>41200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>36200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>38200</v>
       </c>
       <c r="I35" s="3">
         <v>38200</v>
       </c>
       <c r="J35" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K35" s="3">
         <v>34300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>39500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>40500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>46700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>47800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>36500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>49100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>33000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>25500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>126000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>32200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>125300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>26600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>15300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>19800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E41" s="3">
         <v>19100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>39400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>36200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>49100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>133700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>40200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>22300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>65500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>82400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>41200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>25500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>39300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>16700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>184800</v>
+      </c>
+      <c r="E42" s="3">
         <v>77200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>210400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>198100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>155600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>126000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>113500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>91600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>69400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>132900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>113500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>74000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>75000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,52 +4553,55 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>6400</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>28100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>25900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4585,8 +4678,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2779000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2800000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3205200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2825400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2816300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2834000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3281900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2899700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2922800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2921700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3420300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2956800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2968500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2985600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3010000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2898100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3449500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3326000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3012800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2990300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3461600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3031100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3010100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3011500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3608800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3104800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3065600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3088000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,190 +5053,196 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5822700</v>
+      </c>
+      <c r="E47" s="3">
         <v>5850900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5762900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5810200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5592500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5626300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5544300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5793400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5604300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5606400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5520800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5406300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5605200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5733200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6587600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6638000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6936400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7253100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7449500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7531300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7587500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7313100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7262200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7142100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6880800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6601200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6639200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6733000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6419600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>8557800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>8250700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>8242000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8232800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>8224700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>8352300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>8337100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>8237900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>8124300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7999400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>8169200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>70800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>73400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>68600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>11600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
         <v>9000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5153,21 +5261,21 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>16500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>17500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13200</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5177,8 +5285,8 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5195,100 +5303,103 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>546900</v>
+      </c>
+      <c r="E49" s="3">
         <v>549500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>554000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>557700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>554300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>555700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>557300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>559100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>558900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>558300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>560900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>563200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>564900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>567400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>424700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>248500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>252700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>256900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>188900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>192200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>195400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>198700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>201900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>215400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>218900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>222600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>226300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>229900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>29500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>57500</v>
-      </c>
-      <c r="AG49" s="3">
-        <v>47400</v>
       </c>
       <c r="AH49" s="3">
         <v>47400</v>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>47400</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>47400</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,55 +5678,58 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6088500</v>
+      </c>
+      <c r="E52" s="3">
         <v>5530700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5253100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5657300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5429700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5084300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4710400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5188100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4968100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4919400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4149400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4338200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4436200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4265300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15604400</v>
+      </c>
+      <c r="E54" s="3">
         <v>14965900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15266600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15489700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14728300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14396100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14487800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14713600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14282100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14236300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14049900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13412500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13671900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13653900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13306100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13314100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13758500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14427400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14383900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14265000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14190100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13745500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13471800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13003400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12571700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11972200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12478700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12332500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11779400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11561100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11031900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11280800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11156200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11068500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11198300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11044300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10876100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10779500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10576800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10691100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,53 +6145,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>587800</v>
+      </c>
+      <c r="E57" s="3">
         <v>573800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>565200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>564100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>576600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>577100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>569200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>597000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>596600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>584400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>581700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>586600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>597800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>574800</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6137,8 +6268,11 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,11 +6280,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>1014500</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6158,32 +6292,32 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>12000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>249200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>319200</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6226,8 +6360,8 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
+      <c r="AF58" s="3">
+        <v>0</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
@@ -6241,8 +6375,8 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>460100</v>
+      </c>
+      <c r="E59" s="3">
         <v>446400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>483800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>453700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>429100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>413800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>451000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>431500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>401600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>384800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>409300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>296400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>272500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>354900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10858500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3866800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4091400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4476100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4652000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4582500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4531000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4188300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3907200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3505700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3325200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2936800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3434400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3284600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3416400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3326800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3045300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3289100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3174500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3114500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3136800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3030900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2937400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2963700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2879200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>2827300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1047900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1020200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2063500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1017800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1005700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>990900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1032200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1073500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1045100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1019200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>991000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>883200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1119500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1248900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>594200</v>
+      </c>
+      <c r="E61" s="3">
         <v>593800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>618400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>842900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>547500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>547200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1536500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>546700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>546500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>546200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1450500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>546100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>249100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>249000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>498000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>497900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>497800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>502700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>502600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>388600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>413500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>437400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>437300</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>437200</v>
       </c>
       <c r="AA61" s="3">
         <v>437200</v>
       </c>
       <c r="AB61" s="3">
+        <v>437200</v>
+      </c>
+      <c r="AC61" s="3">
         <v>433100</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>433000</v>
       </c>
       <c r="AD61" s="3">
         <v>433000</v>
       </c>
       <c r="AE61" s="3">
+        <v>433000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>297900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>297800</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>297700</v>
       </c>
       <c r="AH61" s="3">
         <v>297700</v>
       </c>
       <c r="AI61" s="3">
+        <v>297700</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>297600</v>
-      </c>
-      <c r="AJ61" s="3">
-        <v>297500</v>
       </c>
       <c r="AK61" s="3">
         <v>297500</v>
       </c>
       <c r="AL61" s="3">
+        <v>297500</v>
+      </c>
+      <c r="AM61" s="3">
         <v>247400</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>247300</v>
       </c>
       <c r="AN61" s="3">
         <v>247300</v>
       </c>
       <c r="AO61" s="3">
+        <v>247300</v>
+      </c>
+      <c r="AP61" s="3">
         <v>247200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>247100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12459400</v>
+      </c>
+      <c r="E62" s="3">
         <v>11881900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11036500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12187700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11814800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11515200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10575800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11806400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11481700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11459500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10399700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10931900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11201400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11016800</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14101500</v>
+      </c>
+      <c r="E66" s="3">
         <v>13495900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13783900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14048400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13368000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13053300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13200300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13426600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13073300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13024900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12874600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12361200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12570000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12514700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12207800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12237500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12498400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12890600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12576500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12468600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12373500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12052600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11681700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11287700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10931900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10494500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10911400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10753900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>10279700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10137400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9741300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9976500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9805800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9663900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9696800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9653900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9514000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>9457700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>9282800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>9247000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1704700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1678000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1651700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1630200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1586500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1571700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1548200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1524100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1504000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1514400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1502200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1476500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1478600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1505200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1512400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1500400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1499900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1525900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1524900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1497500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1494400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1460800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1434600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1399500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1375700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1357800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1352500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1331700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1318300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1236600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1216600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1248800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1248300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1254400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1231200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1165300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1150300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1159500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1155700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1147000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1502900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1470000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1482700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1441300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1360300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1342800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1287500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1287000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1208800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1211400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1175300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1051300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1101900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1139200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1098300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1076600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1260100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1536800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1807400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1796400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1816600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1692900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1790100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1715700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1639800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1477600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1567300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1578600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1499700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1423700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1290600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1304300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1350400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1404700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1501600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1390400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1362100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1321800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1294000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1444100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E81" s="3">
         <v>41200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>36200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>38200</v>
       </c>
       <c r="I81" s="3">
         <v>38200</v>
       </c>
       <c r="J81" s="3">
+        <v>38200</v>
+      </c>
+      <c r="K81" s="3">
         <v>34300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>39500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>40500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>46700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>47800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>36500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>49100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>33000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>25500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>126000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>32200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>125300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>26600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>15300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>19800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,89 +8990,90 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="E83" s="3">
         <v>3400</v>
       </c>
       <c r="F83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G83" s="3">
         <v>2800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3000</v>
       </c>
       <c r="I83" s="3">
         <v>3000</v>
       </c>
       <c r="J83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>5600</v>
       </c>
       <c r="W83" s="3">
         <v>5600</v>
       </c>
       <c r="X83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y83" s="3">
         <v>5500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>5900</v>
       </c>
       <c r="Z83" s="3">
         <v>5900</v>
       </c>
       <c r="AA83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>11700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5300</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>8</v>
       </c>
@@ -8890,8 +9089,8 @@
       <c r="AH83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI83" s="3">
-        <v>0</v>
+      <c r="AI83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ83" s="3">
         <v>0</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E89" s="3">
         <v>61300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>129900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>151200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>131300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>140800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>193500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>143900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>74500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>102900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>45300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>67500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>86400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>55700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>95700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>61500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-25400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>142000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>102200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>165600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>87400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-79700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>109400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>97800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>124800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>66200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>79200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>72100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>19400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>82800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>81700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>72800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>46600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>49100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,8 +9955,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9812,8 +10033,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-102900</v>
+      </c>
+      <c r="E94" s="3">
         <v>16200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-162600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-59500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>50700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-95300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>81300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-78400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-217700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>49000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-103600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-239500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-173900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-195000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-140000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>121600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-88800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>23200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-146200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-71400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-78700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-33700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-41200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-99400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-84300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-95700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-102300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,19 +10455,20 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E96" s="3">
         <v>14600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>14300</v>
       </c>
       <c r="G96" s="3">
         <v>14300</v>
@@ -10243,10 +10477,10 @@
         <v>14300</v>
       </c>
       <c r="I96" s="3">
+        <v>14300</v>
+      </c>
+      <c r="J96" s="3">
         <v>13800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>13900</v>
       </c>
       <c r="K96" s="3">
         <v>13900</v>
@@ -10255,67 +10489,67 @@
         <v>13900</v>
       </c>
       <c r="M96" s="3">
+        <v>13900</v>
+      </c>
+      <c r="N96" s="3">
         <v>13500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>13400</v>
-      </c>
-      <c r="O96" s="3">
-        <v>13500</v>
       </c>
       <c r="P96" s="3">
         <v>13500</v>
       </c>
       <c r="Q96" s="3">
-        <v>-13100</v>
+        <v>13500</v>
       </c>
       <c r="R96" s="3">
         <v>-13100</v>
       </c>
       <c r="S96" s="3">
-        <v>-13200</v>
+        <v>-13100</v>
       </c>
       <c r="T96" s="3">
         <v>-13200</v>
       </c>
       <c r="U96" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-12800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-12900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-12800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-12900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-12400</v>
       </c>
       <c r="Z96" s="3">
         <v>-12400</v>
       </c>
       <c r="AA96" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-23600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-11800</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-11700</v>
       </c>
       <c r="AH96" s="3">
         <v>-11700</v>
@@ -10324,10 +10558,10 @@
         <v>-11700</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-11600</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-11500</v>
       </c>
       <c r="AL96" s="3">
         <v>-11500</v>
@@ -10339,13 +10573,16 @@
         <v>-11500</v>
       </c>
       <c r="AO96" s="3">
-        <v>-11100</v>
+        <v>-11500</v>
       </c>
       <c r="AP96" s="3">
         <v>-11100</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-11100</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-95500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-84100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-387400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>273000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-83800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-113500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-190800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-74500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-85900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-122500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-130400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-49900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>95100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>37400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>17700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-42800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>119000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>114600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>54700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>86300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>68300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-55800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>11200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-125300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>24800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-22100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>22800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>7300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-68500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>12800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-275000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>261600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-84600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>93500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>17100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-43200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>56900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>15700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>31700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-15700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>16300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>9400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-36900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>3200</v>
       </c>
     </row>
